--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Documents\DATA309\Datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\file\Usersd$\dvi21\Home\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800BBA93-AF15-4166-A64F-C05BE77FF71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC67983-C57B-4C78-A0BF-F4FEB3689AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5310" yWindow="2380" windowWidth="16920" windowHeight="10450" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Dataset</t>
   </si>
@@ -99,13 +99,19 @@
   </si>
   <si>
     <t>https://www.qv.co.nz/price-index/</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Descriptive</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,21 +487,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.7265625" customWidth="1"/>
+    <col min="1" max="1" width="28.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -503,7 +512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -511,23 +520,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -535,7 +550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -543,7 +558,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -551,7 +566,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -559,12 +574,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\file\Usersd$\dvi21\Home\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benbirkett/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC67983-C57B-4C78-A0BF-F4FEB3689AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E1D0365-EAEE-BD46-A48E-A52CB8BD7CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="15720" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>Dataset</t>
   </si>
@@ -105,13 +105,34 @@
   </si>
   <si>
     <t>Descriptive</t>
+  </si>
+  <si>
+    <t>Rent Averages in CHCH region</t>
+  </si>
+  <si>
+    <t>https://regions.infometrics.co.nz/canterbury-region/income-and-housing/average-rent?compare=new-zealand,christchurch-city,selwyn-district&amp;average-type=median</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>Internal Migration</t>
+  </si>
+  <si>
+    <t>https://www.stats.govt.nz/information-releases/subnational-population-estimates-at-30-june-2025/</t>
+  </si>
+  <si>
+    <t>RBNZ mortgage interest rate data</t>
+  </si>
+  <si>
+    <t>https://www.rbnz.govt.nz/statistics/series/exchange-and-interest-rates/new-residential-mortgage-standard-interest-rates</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +146,19 @@
       <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF33CCCC"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -149,9 +183,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -168,6 +204,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,13 +527,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.75" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -504,7 +544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -512,7 +552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -531,7 +571,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -542,7 +582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -550,7 +590,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -558,7 +598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -566,7 +606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -574,7 +614,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -583,6 +623,41 @@
       </c>
       <c r="C10" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -596,7 +671,15 @@
     <hyperlink ref="B8" r:id="rId7" xr:uid="{38680BAB-D2B4-4206-92EB-FD27E6076FB8}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{EE6C9D94-14BB-4174-9569-2B379E9F2A58}"/>
     <hyperlink ref="B10" r:id="rId9" xr:uid="{A64392DD-F1D0-4487-AC77-534D20F3FAE3}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{5877F38B-6FA4-7A41-A7A6-D3532C1AB7CA}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{818D9665-82D5-374C-B4A0-1B5C70623F7A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{dc781727-710e-4855-bc4c-690266a1b551}" enabled="0" method="" siteId="{dc781727-710e-4855-bc4c-690266a1b551}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benbirkett/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/DATA309-Housing-Affordability/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E1D0365-EAEE-BD46-A48E-A52CB8BD7CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{9E1D0365-EAEE-BD46-A48E-A52CB8BD7CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64D3FC7B-E82E-4D5E-9B5E-62E3FB4EBAD7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="15720" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>Dataset</t>
   </si>
@@ -126,6 +126,21 @@
   </si>
   <si>
     <t>https://www.rbnz.govt.nz/statistics/series/exchange-and-interest-rates/new-residential-mortgage-standard-interest-rates</t>
+  </si>
+  <si>
+    <t>NZ Population</t>
+  </si>
+  <si>
+    <t>https://infoshare.stats.govt.nz/ViewTable.aspx?pxID=a15bf5ff-20cd-43b8-8314-aa30593e1588</t>
+  </si>
+  <si>
+    <t>Guy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.stats.govt.nz/large-datasets/csv-files-for-download/ </t>
+  </si>
+  <si>
+    <t>Consumer Price Index by Quarter</t>
   </si>
 </sst>
 </file>
@@ -183,11 +198,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -204,10 +223,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -527,13 +542,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -544,7 +559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -552,7 +567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -560,7 +575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -571,7 +586,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -582,7 +597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -590,7 +605,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -598,7 +613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -606,7 +621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -614,7 +629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -625,7 +640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -637,7 +652,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -649,7 +664,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -658,6 +673,28 @@
       </c>
       <c r="C13" s="2" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -673,6 +710,8 @@
     <hyperlink ref="B10" r:id="rId9" xr:uid="{A64392DD-F1D0-4487-AC77-534D20F3FAE3}"/>
     <hyperlink ref="B11" r:id="rId10" xr:uid="{5877F38B-6FA4-7A41-A7A6-D3532C1AB7CA}"/>
     <hyperlink ref="B13" r:id="rId11" xr:uid="{818D9665-82D5-374C-B4A0-1B5C70623F7A}"/>
+    <hyperlink ref="B14" r:id="rId12" xr:uid="{76F49E4C-D6F1-49DE-9CD1-D91CF1D2CF00}"/>
+    <hyperlink ref="B15" r:id="rId13" xr:uid="{B63E88D2-95C9-47DD-8A17-79B2BC8CB12C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/DATA309-Housing-Affordability/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{9E1D0365-EAEE-BD46-A48E-A52CB8BD7CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64D3FC7B-E82E-4D5E-9B5E-62E3FB4EBAD7}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{9E1D0365-EAEE-BD46-A48E-A52CB8BD7CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFFDB6B-CB74-46A0-B0C0-ABE4080B93AB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>Dataset</t>
   </si>
@@ -198,7 +198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -206,7 +206,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -223,6 +222,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -612,6 +615,9 @@
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -620,6 +626,9 @@
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -682,18 +691,18 @@
       <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" t="s">
         <v>31</v>
       </c>
     </row>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/DATA309-Housing-Affordability/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{9E1D0365-EAEE-BD46-A48E-A52CB8BD7CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFFDB6B-CB74-46A0-B0C0-ABE4080B93AB}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{9E1D0365-EAEE-BD46-A48E-A52CB8BD7CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5A8D2C2-68E2-4411-83D0-6F0F87F5C487}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>Dataset</t>
   </si>
@@ -637,6 +637,9 @@
       <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/DATA309-Housing-Affordability/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{9E1D0365-EAEE-BD46-A48E-A52CB8BD7CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5A8D2C2-68E2-4411-83D0-6F0F87F5C487}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3F334EF-8D0F-4D11-A4D4-24E15B8B8E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>Dataset</t>
   </si>
@@ -141,6 +141,24 @@
   </si>
   <si>
     <t>Consumer Price Index by Quarter</t>
+  </si>
+  <si>
+    <t>bright_line_monthly_series</t>
+  </si>
+  <si>
+    <t>compiled</t>
+  </si>
+  <si>
+    <t>monthly_rents</t>
+  </si>
+  <si>
+    <t>https://www.tenancy.govt.nz/about-tenancy-services/data-and-statistics/rental-bond-data/</t>
+  </si>
+  <si>
+    <t>Canterbury_Population</t>
+  </si>
+  <si>
+    <t>https://regions.infometrics.co.nz/canterbury-region/population/growth</t>
   </si>
 </sst>
 </file>
@@ -222,10 +240,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -545,13 +559,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +576,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -570,7 +584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -578,7 +592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -589,7 +603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -600,7 +614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -608,7 +622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -619,7 +633,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -630,7 +644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -641,7 +655,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -652,7 +666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -664,7 +678,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -676,7 +690,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -687,7 +701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -698,7 +712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -707,6 +721,39 @@
       </c>
       <c r="C15" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -724,6 +771,8 @@
     <hyperlink ref="B13" r:id="rId11" xr:uid="{818D9665-82D5-374C-B4A0-1B5C70623F7A}"/>
     <hyperlink ref="B14" r:id="rId12" xr:uid="{76F49E4C-D6F1-49DE-9CD1-D91CF1D2CF00}"/>
     <hyperlink ref="B15" r:id="rId13" xr:uid="{B63E88D2-95C9-47DD-8A17-79B2BC8CB12C}"/>
+    <hyperlink ref="B17" r:id="rId14" xr:uid="{37600B09-268E-4CB3-B02E-848C5B49146C}"/>
+    <hyperlink ref="B18" r:id="rId15" xr:uid="{E978DDFB-A925-48C2-B0A8-8F3F153B9DB6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3F334EF-8D0F-4D11-A4D4-24E15B8B8E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F983C07-B3D8-4DE9-9AC3-00DA8EF45B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>Dataset</t>
   </si>
@@ -159,6 +159,42 @@
   </si>
   <si>
     <t>https://regions.infometrics.co.nz/canterbury-region/population/growth</t>
+  </si>
+  <si>
+    <t>Volume Sold (Time_series_data)</t>
+  </si>
+  <si>
+    <t>https://www.interest.co.nz/charts/real-estate/volumes-sold-reinz</t>
+  </si>
+  <si>
+    <t>Unemployment_rate</t>
+  </si>
+  <si>
+    <t>https://www.stats.govt.nz/indicators/unemployment-rate/</t>
+  </si>
+  <si>
+    <t>mean_income</t>
+  </si>
+  <si>
+    <t>https://regions.infometrics.co.nz/new-zealand/income-and-housing/earnings?compare=new-zealand,canterbury-region</t>
+  </si>
+  <si>
+    <t>LVR</t>
+  </si>
+  <si>
+    <t>https://www.rbnz.govt.nz/statistics/series/lending-and-monetary/new-residential-mortgage-lending-by-loan-to-valuation-ratio</t>
+  </si>
+  <si>
+    <t>https://infoshare.stats.govt.nz/ViewTable.aspx?pxID=d11b838c-706e-4214-a1c8-76c758523185</t>
+  </si>
+  <si>
+    <t>Migration</t>
+  </si>
+  <si>
+    <t>Consents</t>
+  </si>
+  <si>
+    <t>https://infoshare.stats.govt.nz/ViewTable.aspx?pxID=833fb13e-6084-4322-b0e1-90a43f5ae6bd</t>
   </si>
 </sst>
 </file>
@@ -559,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" customWidth="1"/>
@@ -753,6 +789,72 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -773,6 +875,12 @@
     <hyperlink ref="B15" r:id="rId13" xr:uid="{B63E88D2-95C9-47DD-8A17-79B2BC8CB12C}"/>
     <hyperlink ref="B17" r:id="rId14" xr:uid="{37600B09-268E-4CB3-B02E-848C5B49146C}"/>
     <hyperlink ref="B18" r:id="rId15" xr:uid="{E978DDFB-A925-48C2-B0A8-8F3F153B9DB6}"/>
+    <hyperlink ref="B19" r:id="rId16" xr:uid="{1121DC87-D304-4544-B610-6CD39F2394B8}"/>
+    <hyperlink ref="B20" r:id="rId17" xr:uid="{80423C33-7C43-4E16-92E4-28018184DE88}"/>
+    <hyperlink ref="B21" r:id="rId18" xr:uid="{9270ED35-AB84-4E87-9353-B2CF90DD92EF}"/>
+    <hyperlink ref="B22" r:id="rId19" xr:uid="{7F800375-5488-485F-AD2F-19FB76FE2572}"/>
+    <hyperlink ref="B23" r:id="rId20" xr:uid="{DAE6FD5A-D05F-4E32-9D1D-7178DCC6AC95}"/>
+    <hyperlink ref="B24" r:id="rId21" xr:uid="{770D3267-F733-4360-9271-7A7D0936D32A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F983C07-B3D8-4DE9-9AC3-00DA8EF45B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F4632B-5955-4598-A61B-A3CAECAD83B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
   <si>
     <t>Dataset</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>https://infoshare.stats.govt.nz/ViewTable.aspx?pxID=833fb13e-6084-4322-b0e1-90a43f5ae6bd</t>
+  </si>
+  <si>
+    <t>Private_dwellings</t>
+  </si>
+  <si>
+    <t>https://infoshare.stats.govt.nz/ViewTable.aspx?pxID=27bd7db6-d68f-432d-b391-9633572ec1f9</t>
   </si>
 </sst>
 </file>
@@ -595,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" customWidth="1"/>
@@ -855,6 +861,17 @@
         <v>51</v>
       </c>
       <c r="C24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
         <v>20</v>
       </c>
     </row>
@@ -881,6 +898,7 @@
     <hyperlink ref="B22" r:id="rId19" xr:uid="{7F800375-5488-485F-AD2F-19FB76FE2572}"/>
     <hyperlink ref="B23" r:id="rId20" xr:uid="{DAE6FD5A-D05F-4E32-9D1D-7178DCC6AC95}"/>
     <hyperlink ref="B24" r:id="rId21" xr:uid="{770D3267-F733-4360-9271-7A7D0936D32A}"/>
+    <hyperlink ref="B25" r:id="rId22" xr:uid="{7F82E472-66CA-4D02-9BC2-C247CCF27354}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F4632B-5955-4598-A61B-A3CAECAD83B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCDFD9C-E8F2-4590-ABA4-B2E39C30DC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="5810" yWindow="0" windowWidth="16920" windowHeight="10450" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>Dataset</t>
   </si>
@@ -183,12 +183,6 @@
   </si>
   <si>
     <t>https://www.rbnz.govt.nz/statistics/series/lending-and-monetary/new-residential-mortgage-lending-by-loan-to-valuation-ratio</t>
-  </si>
-  <si>
-    <t>https://infoshare.stats.govt.nz/ViewTable.aspx?pxID=d11b838c-706e-4214-a1c8-76c758523185</t>
-  </si>
-  <si>
-    <t>Migration</t>
   </si>
   <si>
     <t>Consents</t>
@@ -601,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" customWidth="1"/>
@@ -844,10 +838,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
@@ -861,17 +855,6 @@
         <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" t="s">
         <v>20</v>
       </c>
     </row>
@@ -896,9 +879,8 @@
     <hyperlink ref="B20" r:id="rId17" xr:uid="{80423C33-7C43-4E16-92E4-28018184DE88}"/>
     <hyperlink ref="B21" r:id="rId18" xr:uid="{9270ED35-AB84-4E87-9353-B2CF90DD92EF}"/>
     <hyperlink ref="B22" r:id="rId19" xr:uid="{7F800375-5488-485F-AD2F-19FB76FE2572}"/>
-    <hyperlink ref="B23" r:id="rId20" xr:uid="{DAE6FD5A-D05F-4E32-9D1D-7178DCC6AC95}"/>
-    <hyperlink ref="B24" r:id="rId21" xr:uid="{770D3267-F733-4360-9271-7A7D0936D32A}"/>
-    <hyperlink ref="B25" r:id="rId22" xr:uid="{7F82E472-66CA-4D02-9BC2-C247CCF27354}"/>
+    <hyperlink ref="B23" r:id="rId20" xr:uid="{770D3267-F733-4360-9271-7A7D0936D32A}"/>
+    <hyperlink ref="B24" r:id="rId21" xr:uid="{7F82E472-66CA-4D02-9BC2-C247CCF27354}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lumpy\OneDrive\Documents\Vault For Conor\Vault For Conor\Courses\3.2\DATA309\Assesments\DATA309-Housing-Affordability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCDFD9C-E8F2-4590-ABA4-B2E39C30DC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D73B0D5-A26F-4E95-B49C-9F93DE84EC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5810" yWindow="0" windowWidth="16920" windowHeight="10450" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
   <si>
     <t>Dataset</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>https://infoshare.stats.govt.nz/ViewTable.aspx?pxID=27bd7db6-d68f-432d-b391-9633572ec1f9</t>
+  </si>
+  <si>
+    <t>Conor</t>
+  </si>
+  <si>
+    <t>nz-properties-national-district-valuation-roll.csv</t>
   </si>
 </sst>
 </file>
@@ -595,13 +601,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6328125" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -612,7 +619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -620,7 +627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -628,7 +635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -639,7 +646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -649,8 +656,11 @@
       <c r="C5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -658,7 +668,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -669,7 +679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -680,7 +690,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -691,7 +701,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -702,7 +712,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -714,7 +724,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -726,7 +736,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -737,7 +747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -748,7 +758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -759,7 +769,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -770,7 +780,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -781,7 +791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -792,7 +802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -803,7 +813,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -814,7 +824,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -825,7 +835,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -836,7 +846,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -847,7 +857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -856,6 +866,17 @@
       </c>
       <c r="C24" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -881,6 +902,7 @@
     <hyperlink ref="B22" r:id="rId19" xr:uid="{7F800375-5488-485F-AD2F-19FB76FE2572}"/>
     <hyperlink ref="B23" r:id="rId20" xr:uid="{770D3267-F733-4360-9271-7A7D0936D32A}"/>
     <hyperlink ref="B24" r:id="rId21" xr:uid="{7F82E472-66CA-4D02-9BC2-C247CCF27354}"/>
+    <hyperlink ref="B25" r:id="rId22" xr:uid="{4C278FE6-A58C-4500-B039-212F4C751DA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lumpy\OneDrive\Documents\Vault For Conor\Vault For Conor\Courses\3.2\DATA309\Assesments\DATA309-Housing-Affordability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D73B0D5-A26F-4E95-B49C-9F93DE84EC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE0C018-25B6-4697-97F1-A4C1C36C2C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t>Dataset</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>nz-properties-national-district-valuation-roll.csv</t>
+  </si>
+  <si>
+    <t>compiled from 03_01_Analysis</t>
+  </si>
+  <si>
+    <t>ecan_classified.csv</t>
   </si>
 </sst>
 </file>
@@ -601,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
@@ -876,6 +882,17 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" t="s">
         <v>52</v>
       </c>
     </row>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lumpy\OneDrive\Documents\Vault For Conor\Vault For Conor\Courses\3.2\DATA309\Assesments\DATA309-Housing-Affordability\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE0C018-25B6-4697-97F1-A4C1C36C2C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9DF43D-C601-477B-8858-67877978C25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
   <si>
     <t>Dataset</t>
   </si>
@@ -197,16 +197,10 @@
     <t>https://infoshare.stats.govt.nz/ViewTable.aspx?pxID=27bd7db6-d68f-432d-b391-9633572ec1f9</t>
   </si>
   <si>
-    <t>Conor</t>
-  </si>
-  <si>
-    <t>nz-properties-national-district-valuation-roll.csv</t>
-  </si>
-  <si>
-    <t>compiled from 03_01_Analysis</t>
-  </si>
-  <si>
-    <t>ecan_classified.csv</t>
+    <t>https://www.interest.co.nz/Charts/Real%20estate/Housing%20inventory</t>
+  </si>
+  <si>
+    <t>Housing Inventory (Time_series_data)</t>
   </si>
 </sst>
 </file>
@@ -607,14 +601,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -625,7 +618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -633,7 +626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -641,7 +634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -652,7 +645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -662,11 +655,8 @@
       <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -674,7 +664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -685,7 +675,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -696,7 +686,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -707,7 +697,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -718,7 +708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -730,7 +720,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -742,7 +732,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -753,7 +743,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -764,7 +754,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -775,7 +765,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -786,7 +776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -797,7 +787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -808,7 +798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -819,7 +809,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -830,7 +820,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -841,7 +831,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -852,7 +842,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -863,7 +853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -874,26 +864,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -919,7 +898,7 @@
     <hyperlink ref="B22" r:id="rId19" xr:uid="{7F800375-5488-485F-AD2F-19FB76FE2572}"/>
     <hyperlink ref="B23" r:id="rId20" xr:uid="{770D3267-F733-4360-9271-7A7D0936D32A}"/>
     <hyperlink ref="B24" r:id="rId21" xr:uid="{7F82E472-66CA-4D02-9BC2-C247CCF27354}"/>
-    <hyperlink ref="B25" r:id="rId22" xr:uid="{4C278FE6-A58C-4500-B039-212F4C751DA6}"/>
+    <hyperlink ref="B25" r:id="rId22" xr:uid="{F80CCCBA-DD9F-41C2-8065-9C1B01B5C0CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset_sources.xlsx
+++ b/dataset_sources.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lumpy\Conor Obsidian\Courses\3.2\DATA309\Assesments\DATA309-Housing-Affordability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9DF43D-C601-477B-8858-67877978C25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A26187E-550A-4F11-9671-22B95EB4E6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
+    <workbookView xWindow="32940" yWindow="285" windowWidth="23985" windowHeight="15195" xr2:uid="{BF2979F8-E01C-472F-8015-CA294AC08A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="58">
   <si>
     <t>Dataset</t>
   </si>
@@ -201,6 +202,18 @@
   </si>
   <si>
     <t>Housing Inventory (Time_series_data)</t>
+  </si>
+  <si>
+    <t>Uses</t>
+  </si>
+  <si>
+    <t>data_urban_rural_locality_lookup.csv</t>
+  </si>
+  <si>
+    <t>Conor</t>
+  </si>
+  <si>
+    <t>derived lookup</t>
   </si>
 </sst>
 </file>
@@ -601,13 +614,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061C0C33-7D3C-4AAD-B222-7BF2650F4FDB}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6328125" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -618,23 +632,29 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -644,8 +664,11 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -656,7 +679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -664,7 +687,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -675,7 +698,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -686,7 +709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -697,7 +720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -708,7 +731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -720,7 +743,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -732,7 +755,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -743,7 +766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -754,7 +777,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -765,7 +788,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -776,7 +799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -787,7 +810,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -798,7 +821,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -809,7 +832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -820,7 +843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -831,7 +854,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -842,7 +865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -853,7 +876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -864,7 +887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -873,6 +896,17 @@
       </c>
       <c r="C25" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -901,6 +935,315 @@
     <hyperlink ref="B25" r:id="rId22" xr:uid="{F80CCCBA-DD9F-41C2-8065-9C1B01B5C0CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66E3060-C138-4E5A-BA47-28C9B83F6AB1}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.85546875" customWidth="1"/>
+    <col min="5" max="5" width="39.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{7D8B746B-7579-4696-83D3-C3E29B92EC91}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{D4131088-AB06-4F2F-9A4D-D9CB4FF3F409}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{75F78F8E-633E-4AF1-BBD8-6255F1C9D5C1}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{8A666893-E733-4858-8233-D573B9A37C5E}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{95CB0180-7052-419A-8ABE-3F10FDE6DF59}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{B0478B8F-36B9-4B34-AC2B-8AE24D00EA37}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{B25BBDA1-F1C8-4935-977A-072D5D2E826F}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{570BCFB0-0C68-4022-A64B-CA6006FFF6CF}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{2EDFA51C-220F-4D2C-8C8D-954A0C026BCA}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{39A55675-C353-4DAF-AA5F-88583A095266}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{0EF58D33-6DA3-420A-A87D-86CC5A3101C7}"/>
+    <hyperlink ref="B14" r:id="rId12" xr:uid="{A221E349-5677-4487-8968-1F4553A5D945}"/>
+    <hyperlink ref="B15" r:id="rId13" xr:uid="{FC38D041-1A4E-4B68-96B9-E3C8BC787D88}"/>
+    <hyperlink ref="B17" r:id="rId14" xr:uid="{89F300D8-9FCF-4B62-A48F-276864DD320C}"/>
+    <hyperlink ref="B18" r:id="rId15" xr:uid="{EEB685F0-C0BB-4F21-B0B0-AB7322646A9F}"/>
+    <hyperlink ref="B19" r:id="rId16" xr:uid="{2E46284C-7473-4925-B864-C2B8D0F00D64}"/>
+    <hyperlink ref="B20" r:id="rId17" xr:uid="{B3B5F302-192D-46B8-8F8B-529D320693BA}"/>
+    <hyperlink ref="B21" r:id="rId18" xr:uid="{BAE883D8-58DE-4696-A994-F5F747AE4D77}"/>
+    <hyperlink ref="B22" r:id="rId19" xr:uid="{7FA3E9A6-5E1F-4B3C-8A1C-FD2963822431}"/>
+    <hyperlink ref="B23" r:id="rId20" xr:uid="{C17B9075-B376-4EC2-8FA0-0C15E6E294F3}"/>
+    <hyperlink ref="B24" r:id="rId21" xr:uid="{DF9C8A8C-D826-4269-8F3F-FD901BF8CECB}"/>
+    <hyperlink ref="B25" r:id="rId22" xr:uid="{DAFE827A-EE97-45FF-8278-A0924914C6A5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
